--- a/박소희.xlsx
+++ b/박소희.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4939F833-CC8D-4EDA-B1FE-7C2DBB56F951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BA8DD6-8B11-4621-B9D1-698000DBB298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>교시</t>
   </si>
@@ -79,13 +79,17 @@
   </si>
   <si>
     <t>8(16:00)</t>
+  </si>
+  <si>
+    <t>동아리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +110,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -183,7 +194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -196,6 +207,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -205,10 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -549,14 +563,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="5"/>
       <c r="C2" s="2">
         <v>302</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="2">
         <v>205</v>
       </c>
@@ -565,12 +579,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
@@ -579,7 +593,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
@@ -599,7 +613,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
@@ -620,17 +634,17 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="2">
         <v>108</v>
       </c>
@@ -645,8 +659,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
@@ -661,58 +675,62 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>107</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>106</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="2">
         <v>309</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="2">
         <v>302</v>
       </c>
@@ -722,11 +740,11 @@
       <c r="E13" s="2">
         <v>309</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
@@ -736,20 +754,29 @@
       <c r="E14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F11:F12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="A7:A8"/>
@@ -759,15 +786,6 @@
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="F13:F14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
